--- a/output/pdf_financials_xlsx/MTL.xlsx
+++ b/output/pdf_financials_xlsx/MTL.xlsx
@@ -2030,52 +2030,52 @@
         <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0</v>
+        <v>0.08018400000000001</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0</v>
+        <v>76.474</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>0</v>
+        <v>80.818</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>83.669</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>16.743</v>
+        <v>86.242</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>284.741</v>
+        <v>85.161</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>229.419</v>
+        <v>94.247</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>181.033</v>
+        <v>85.3</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.172158</v>
+        <v>0.08656999999999999</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.189015</v>
+        <v>0.087489</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0.200912</v>
+        <v>0.111491</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0.236378</v>
+        <v>0.113964</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0.329889</v>
+        <v>0.112513</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0.328185</v>
+        <v>0.115889</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0.3322</v>
+        <v>0.130903</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>0.315637</v>
+        <v>0.146368</v>
       </c>
     </row>
     <row r="29">
@@ -2088,52 +2088,52 @@
         <v>-0.779</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-16.733</v>
+        <v>-16.652816</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>105.645</v>
+        <v>182.119</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>159.198</v>
+        <v>240.016</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>175.767</v>
+        <v>259.436</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>209.445</v>
+        <v>278.944</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>416.484</v>
+        <v>216.904</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>272.786</v>
+        <v>137.614</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>252.778</v>
+        <v>157.045</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.254444</v>
+        <v>0.168856</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.162422</v>
+        <v>0.060896</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.281049</v>
+        <v>0.191628</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.332373</v>
+        <v>0.209959</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.54077</v>
+        <v>0.323394</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.511325</v>
+        <v>0.299029</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.485966</v>
+        <v>0.284669</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>0.435457</v>
+        <v>0.266188</v>
       </c>
     </row>
     <row r="30">
@@ -2146,52 +2146,52 @@
         <v>-2.857142857142857</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-1710.860225388172</v>
+        <v>-1702.66183799126</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>10.16678551734691</v>
+        <v>17.52628909682144</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>11.47544174157874</v>
+        <v>17.30103157732361</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>12.31171723964025</v>
+        <v>18.17236838418649</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>14.57347307130839</v>
+        <v>19.40930971091718</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>29.16858971979569</v>
+        <v>15.19094079144112</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>22.46313320794616</v>
+        <v>11.33211240048354</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>24.42160301973124</v>
+        <v>15.172565042186</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>22.3492717101351</v>
+        <v>14.83158818398772</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>12.88247601915612</v>
+        <v>4.829956900312342</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>21.98267972987136</v>
+        <v>14.98847870398325</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>22.49663944379241</v>
+        <v>14.21105782051855</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>27.04589705284396</v>
+        <v>16.17412362281084</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>25.63391070731195</v>
+        <v>14.99101879410704</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>24.42957230679054</v>
+        <v>14.31034664771148</v>
       </c>
       <c r="R30" s="3" t="n">
-        <v>20.40909393422139</v>
+        <v>12.47575741384918</v>
       </c>
     </row>
     <row r="31">
@@ -6156,25 +6156,25 @@
         <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>0.08018400000000001</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>76.474</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>80.818</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>83.669</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>86.242</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>85.161</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>94.247</v>
       </c>
       <c r="J100" s="3" t="n">
         <v>85.3</v>
@@ -34109,7 +34109,11 @@
           <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -34210,7 +34214,7 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
@@ -34970,7 +34974,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -35069,7 +35077,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -36633,7 +36641,11 @@
           <t>Depreciation on property, plant and equipment</t>
         </is>
       </c>
-      <c r="D294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
           <t>-</t>
@@ -36728,7 +36740,11 @@
           <t>Amortization on intangible assets</t>
         </is>
       </c>
-      <c r="D295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
           <t>-</t>
@@ -37522,7 +37538,11 @@
           <t>Depreciation on property, plant and equipment</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
           <t>-</t>
@@ -37621,7 +37641,11 @@
           <t>Amortization on intangible assets</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -42963,7 +42987,11 @@
           <t>Depreciation of property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D358" t="inlineStr"/>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E358" t="inlineStr">
         <is>
           <t>-</t>
@@ -43038,7 +43066,11 @@
           <t>Depreciation of right-of-use assets 10</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -43127,7 +43159,7 @@
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
@@ -47588,7 +47620,7 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
@@ -48946,7 +48978,11 @@
           <t>Depreciation on property, plant and equipment 9</t>
         </is>
       </c>
-      <c r="D421" t="inlineStr"/>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E421" t="inlineStr">
         <is>
           <t>-</t>
@@ -49037,7 +49073,11 @@
           <t>Amortization on intangible assets 11</t>
         </is>
       </c>
-      <c r="D422" t="inlineStr"/>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E422" t="inlineStr">
         <is>
           <t>-</t>
@@ -51306,7 +51346,11 @@
           <t>Depreciation on property, plant and equipment</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
@@ -51401,7 +51445,11 @@
           <t>Amortization on intangible assets</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MTL.xlsx
+++ b/output/pdf_financials_xlsx/MTL.xlsx
@@ -1319,7 +1319,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>1.682</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>16.82381</v>
@@ -1560,10 +1560,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>0.903</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>0.09081</v>
@@ -1737,7 +1735,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>-0.779</v>
+        <v>0.903</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>0.09081</v>
@@ -1911,7 +1909,7 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-25.966667</v>
+        <v>30.1</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>0.082555</v>
@@ -2201,7 +2199,7 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-215.9178433889602</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-100.5427000537859</v>
@@ -2259,7 +2257,7 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>-2.857142857142857</v>
+        <v>3.31193838254172</v>
       </c>
       <c r="C32" s="3" t="n">
         <v>9.284839363383727</v>
@@ -2681,25 +2679,25 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>22.93</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>15.828</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>21.513</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>13.754</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>18.82</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>11.058</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>14.287</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>0</v>
@@ -2739,25 +2737,25 @@
         <v>151.049</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>262.587</v>
+        <v>285.517</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>219.423</v>
+        <v>235.251</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>234.485</v>
+        <v>255.998</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>209.835</v>
+        <v>223.589</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>159.963</v>
+        <v>178.783</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>153.766</v>
+        <v>164.824</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.175303</v>
+        <v>14.462303</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>0.218089</v>
@@ -3145,25 +3143,25 @@
         <v>8.128</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>11.414</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>12.746</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>17.264</v>
+        <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>15.845</v>
+        <v>2.091</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>15.639</v>
+        <v>0</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>15.065</v>
+        <v>4.007</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.018066</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.016242</v>
@@ -6095,7 +6093,7 @@
         </is>
       </c>
       <c r="B99" s="3" t="n">
-        <v>-0.779</v>
+        <v>0.903</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>0.09081</v>
@@ -6122,7 +6120,7 @@
         <v>52.038</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>65.509</v>
+        <v>0.065509</v>
       </c>
       <c r="L99" s="3" t="n">
         <v>-0.043787</v>
@@ -7029,7 +7027,7 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>2.826</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
@@ -7065,13 +7063,13 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>0.001868</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>6.999999999999999e-05</v>
       </c>
       <c r="R115" s="3" t="n">
-        <v>0</v>
+        <v>6.499999999999999e-05</v>
       </c>
     </row>
     <row r="116">
@@ -7111,10 +7109,10 @@
         <v>0</v>
       </c>
       <c r="L116" s="3" t="n">
-        <v>0</v>
+        <v>-0.002975</v>
       </c>
       <c r="M116" s="3" t="n">
-        <v>0</v>
+        <v>-0.00036</v>
       </c>
       <c r="N116" s="3" t="n">
         <v>0</v>
@@ -7126,7 +7124,7 @@
         <v>0</v>
       </c>
       <c r="Q116" s="3" t="n">
-        <v>0</v>
+        <v>-5e-05</v>
       </c>
       <c r="R116" s="3" t="n">
         <v>0</v>
@@ -7377,7 +7375,7 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-27.276</v>
       </c>
       <c r="E121" s="3" t="n">
         <v>0</v>
@@ -7407,19 +7405,19 @@
         <v>0</v>
       </c>
       <c r="N121" s="3" t="n">
-        <v>0</v>
+        <v>-0.044329</v>
       </c>
       <c r="O121" s="3" t="n">
-        <v>0</v>
+        <v>-0.022921</v>
       </c>
       <c r="P121" s="3" t="n">
-        <v>0</v>
+        <v>-0.072048</v>
       </c>
       <c r="Q121" s="3" t="n">
-        <v>0</v>
+        <v>-0.00649</v>
       </c>
       <c r="R121" s="3" t="n">
-        <v>0</v>
+        <v>-0.01146</v>
       </c>
     </row>
     <row r="122">
@@ -25352,7 +25350,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr"/>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E175" t="inlineStr">
         <is>
           <t>-</t>
@@ -25678,7 +25680,11 @@
           <t>Repurchase of Common Shares 21</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>
@@ -27010,7 +27016,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
           <t>-</t>
@@ -28299,7 +28309,11 @@
           <t>Repurchase of Common Shares 21</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -29124,7 +29138,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -29466,7 +29484,11 @@
           <t>Proceeds on sale of investments 13</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -30617,7 +30639,11 @@
           <t>Repurchase of Common Shares 22</t>
         </is>
       </c>
-      <c r="D232" t="inlineStr"/>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -31189,7 +31215,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -37134,7 +37164,11 @@
           <t>Repurchase of Common Shares</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
           <t>-</t>
@@ -37235,7 +37269,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
           <t>-</t>
@@ -39142,7 +39180,11 @@
           <t>Net proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E319" t="inlineStr">
         <is>
           <t>-</t>
@@ -39443,7 +39485,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
@@ -40047,7 +40093,11 @@
           <t>Proceeds on sale of investments</t>
         </is>
       </c>
-      <c r="D328" t="inlineStr"/>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E328" t="inlineStr">
         <is>
           <t>-</t>
@@ -54942,7 +54992,11 @@
           <t>Net earnings (loss)</t>
         </is>
       </c>
-      <c r="D481" t="inlineStr"/>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E481" s="5" t="n">
         <v>0.903</v>
       </c>
